--- a/data/信用债发行汇总_2026-08-07.xlsx
+++ b/data/信用债发行汇总_2026-08-07.xlsx
@@ -720,7 +720,11 @@
           <t>26国耀融汇CP001</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>042680279.IB</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>0.93Y</t>
@@ -1150,7 +1154,11 @@
           <t>26国耀融汇CP001</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>042680279.IB</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>0.93Y</t>
@@ -1516,7 +1524,9 @@
           <t>1.75 ~ 2.75</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
+        <v>2.53</v>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>西安高新控股有限公司</t>
@@ -1686,7 +1696,9 @@
           <t>2.06 ~ 2.36</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="n">
+        <v>2.36</v>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>珠海华发集团有限公司</t>
